--- a/src/citys/villes_canada.xlsx
+++ b/src/citys/villes_canada.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\DNS\src\citys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAB0D40-CD07-4F64-9119-44F5FA25DD85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B626D347-71A2-4495-9FC5-BCA9560E3065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Top 100 Canada" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
     <t>Toronto</t>
   </si>
   <si>
-    <t>Montréal</t>
-  </si>
-  <si>
     <t>Québec</t>
   </si>
   <si>
@@ -329,6 +326,9 @@
   </si>
   <si>
     <t>North Bay</t>
+  </si>
+  <si>
+    <t>Montreal</t>
   </si>
 </sst>
 </file>
@@ -669,13 +669,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -683,7 +683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -691,793 +691,793 @@
         <v>2794356</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="B3">
         <v>1762949</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>1306784</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1017449</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>1010899</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>749607</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>717961</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>662248</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>656480</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>569353</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>568322</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13">
         <v>549459</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>439819</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>438366</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>422324</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>338503</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>323103</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>291041</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>266141</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <v>256885</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22">
         <v>254483</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23">
         <v>249125</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24">
         <v>229660</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
         <v>226404</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
         <v>213759</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
         <v>209937</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>202022</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>186948</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>175383</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31">
         <v>172950</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32">
         <v>166004</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33">
         <v>153524</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34">
         <v>149683</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35">
         <v>148625</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36">
         <v>147829</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37">
         <v>144723</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38">
         <v>144576</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39">
         <v>143740</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40">
         <v>139163</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41">
         <v>138501</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42">
         <v>138479</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43">
         <v>136803</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44">
         <v>132979</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45">
         <v>132603</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46">
         <v>132485</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47">
         <v>126666</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48">
         <v>121436</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49">
         <v>119944</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50">
         <v>117735</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51">
         <v>110525</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52">
         <v>108843</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53">
         <v>108455</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54">
         <v>104688</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55">
         <v>103988</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56">
         <v>101427</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57">
         <v>100844</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58">
         <v>99863</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59">
         <v>99225</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60">
         <v>99186</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61">
         <v>98406</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62">
         <v>97902</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63">
         <v>97873</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64">
         <v>94415</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65">
         <v>93694</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66">
         <v>93203</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B67">
         <v>91867</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B68">
         <v>91525</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B69">
         <v>90990</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B70">
         <v>88168</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71">
         <v>87942</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B72">
         <v>86100</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73">
         <v>83651</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B74">
         <v>80213</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B75">
         <v>79470</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76">
         <v>79258</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77">
         <v>79247</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78">
         <v>78916</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B79">
         <v>76708</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80">
         <v>76581</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B81">
         <v>74100</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82">
         <v>72326</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B83">
         <v>72051</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B84">
         <v>72047</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B85">
         <v>69895</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B86">
         <v>69025</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B87">
         <v>68232</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B88">
         <v>67490</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B89">
         <v>64141</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B90">
         <v>63271</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B91">
         <v>63116</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B92">
         <v>62951</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B93">
         <v>62057</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B94">
         <v>61498</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B95">
         <v>61108</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96">
         <v>59819</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B97">
         <v>58120</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98">
         <v>57239</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B99">
         <v>55750</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B100">
         <v>55071</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101">
         <v>52662</v>
